--- a/Eval/example_results_IEI.xlsx
+++ b/Eval/example_results_IEI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Metrics</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>VIPER</t>
+  </si>
+  <si>
+    <t>GeneT</t>
   </si>
   <si>
     <t>Xrare</t>
@@ -87,11 +90,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -696,7 +700,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -707,6 +711,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1237,15 +1247,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="5" width="12.8181818181818"/>
-    <col min="6" max="6" width="11.7272727272727"/>
-    <col min="7" max="7" width="12.8181818181818"/>
+    <col min="2" max="6" width="12.8181818181818"/>
+    <col min="7" max="7" width="11.7272727272727"/>
+    <col min="8" max="8" width="12.8181818181818"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1267,10 +1277,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>0.988372093023256</v>
@@ -1278,46 +1291,52 @@
       <c r="C2" s="2">
         <v>0.87984496124031</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
+      <c r="D2" s="2">
+        <v>0.906976744186046</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4">
         <v>183.872146118721</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <f>3566/219</f>
         <v>16.2831050228311</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
+        <v>23.0146341463415</v>
+      </c>
+      <c r="E3" s="4">
         <v>110.985365853659</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="4">
         <v>1353.77073170732</v>
       </c>
-      <c r="F3">
+      <c r="G3" s="5">
         <v>2855.3512195122</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="4">
         <v>2009.53170731707</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2">
         <v>0.0310077519379845</v>
@@ -1326,21 +1345,24 @@
         <v>0.697674418604651</v>
       </c>
       <c r="D4" s="2">
+        <v>0.515503875968992</v>
+      </c>
+      <c r="E4" s="2">
         <v>0.255813953488372</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>0.453488372093023</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G4" s="6">
         <v>0.294573643410853</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="6">
         <v>0.507751937984496</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
         <v>0.205426356589147</v>
@@ -1349,21 +1371,24 @@
         <v>0.848837209302326</v>
       </c>
       <c r="D5" s="2">
+        <v>0.802325581395349</v>
+      </c>
+      <c r="E5" s="2">
         <v>0.538759689922481</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>0.751937984496124</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="6">
         <v>0.538759689922481</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="6">
         <v>0.720930232558139</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>0.325581395348837</v>
@@ -1372,21 +1397,24 @@
         <v>0.926356589147287</v>
       </c>
       <c r="D6" s="2">
+        <v>0.86046511627907</v>
+      </c>
+      <c r="E6" s="2">
         <v>0.693798449612403</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>0.813953488372093</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="6">
         <v>0.651162790697674</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="6">
         <v>0.763565891472868</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>0.488372093023256</v>
@@ -1395,21 +1423,24 @@
         <v>0.957364341085271</v>
       </c>
       <c r="D7" s="2">
+        <v>0.903100775193798</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.75968992248062</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>0.852713178294574</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="6">
         <v>0.701550387596899</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="6">
         <v>0.844961240310077</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>0.651162790697674</v>
@@ -1418,21 +1449,24 @@
         <v>0.988372093023256</v>
       </c>
       <c r="D8" s="2">
+        <v>0.968992248062015</v>
+      </c>
+      <c r="E8" s="2">
         <v>0.806201550387597</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>0.914728682170543</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="6">
         <v>0.844961240310077</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="6">
         <v>0.934108527131783</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>0.782945736434108</v>
@@ -1441,21 +1475,24 @@
         <v>0.996124031007752</v>
       </c>
       <c r="D9" s="2">
+        <v>0.976744186046512</v>
+      </c>
+      <c r="E9" s="2">
         <v>0.887596899224806</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>0.918604651162791</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="6">
         <v>0.875968992248062</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="6">
         <v>0.957364341085271</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
         <v>0.833333333333333</v>
@@ -1464,21 +1501,24 @@
         <v>1</v>
       </c>
       <c r="D10" s="2">
+        <v>0.98062015503876</v>
+      </c>
+      <c r="E10" s="2">
         <v>0.941860465116279</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>0.922480620155039</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="6">
         <v>0.887596899224806</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="6">
         <v>0.957364341085271</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
         <v>0.968992248062015</v>
@@ -1487,15 +1527,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
+        <v>0.988372093023256</v>
+      </c>
+      <c r="E11" s="2">
         <v>0.996124031007752</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>0.945736434108527</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="6">
         <v>0.918604651162791</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="6">
         <v>0.968992248062015</v>
       </c>
     </row>
